--- a/artfynd/A 14999-2024 artfynd.xlsx
+++ b/artfynd/A 14999-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129683585</v>
       </c>
       <c r="B2" t="n">
-        <v>56912</v>
+        <v>56916</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14999-2024 artfynd.xlsx
+++ b/artfynd/A 14999-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129683585</v>
       </c>
       <c r="B2" t="n">
-        <v>56916</v>
+        <v>56917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14999-2024 artfynd.xlsx
+++ b/artfynd/A 14999-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129683585</v>
       </c>
       <c r="B2" t="n">
-        <v>56917</v>
+        <v>56918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14999-2024 artfynd.xlsx
+++ b/artfynd/A 14999-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129683585</v>
       </c>
       <c r="B2" t="n">
-        <v>56918</v>
+        <v>56921</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14999-2024 artfynd.xlsx
+++ b/artfynd/A 14999-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,891 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130215155</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80228</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>747903</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7455922</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Hanna Vestman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130213934</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97704</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>747737</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7456048</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130215250</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91661</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>747925</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7455943</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Hanna Vestman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130213901</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96071</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>747739</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7456070</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130212863</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92948</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellodon fuligineoalbus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>747530</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7456067</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jennifer Sondell</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130213671</v>
+      </c>
+      <c r="B8" t="n">
+        <v>105885</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>747707</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7456091</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130215252</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79095</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>747913</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7455917</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Hanna Vestman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130214040</v>
+      </c>
+      <c r="B10" t="n">
+        <v>96059</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>747784</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7456011</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130213978</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97710</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>747720</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7456169</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14999-2024 artfynd.xlsx
+++ b/artfynd/A 14999-2024 artfynd.xlsx
@@ -1184,32 +1184,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130212863</v>
+        <v>130213671</v>
       </c>
       <c r="B7" t="n">
-        <v>92948</v>
+        <v>105885</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3100</v>
+        <v>221725</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>747530</v>
+        <v>747707</v>
       </c>
       <c r="R7" t="n">
-        <v>7456067</v>
+        <v>7456091</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1274,43 +1274,39 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jennifer Sondell</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
-        </is>
-      </c>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130213671</v>
+        <v>130212863</v>
       </c>
       <c r="B8" t="n">
-        <v>105885</v>
+        <v>92948</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221725</v>
+        <v>3100</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1320,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>747707</v>
+        <v>747530</v>
       </c>
       <c r="R8" t="n">
-        <v>7456091</v>
+        <v>7456067</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1375,10 +1371,14 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Irma Lindfors</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Jennifer Sondell</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">

--- a/artfynd/A 14999-2024 artfynd.xlsx
+++ b/artfynd/A 14999-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>130215155</v>
       </c>
       <c r="B3" t="n">
-        <v>80228</v>
+        <v>80313</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>130213934</v>
       </c>
       <c r="B4" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>130215250</v>
       </c>
       <c r="B5" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>130213901</v>
       </c>
       <c r="B6" t="n">
-        <v>96071</v>
+        <v>96158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,32 +1184,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130213671</v>
+        <v>130212863</v>
       </c>
       <c r="B7" t="n">
-        <v>105885</v>
+        <v>93035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221725</v>
+        <v>3100</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>747707</v>
+        <v>747530</v>
       </c>
       <c r="R7" t="n">
-        <v>7456091</v>
+        <v>7456067</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1274,39 +1274,43 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Irma Lindfors</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Jennifer Sondell</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130212863</v>
+        <v>130213671</v>
       </c>
       <c r="B8" t="n">
-        <v>92948</v>
+        <v>105972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3100</v>
+        <v>221725</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>747530</v>
+        <v>747707</v>
       </c>
       <c r="R8" t="n">
-        <v>7456067</v>
+        <v>7456091</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1371,21 +1375,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jennifer Sondell</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
-        </is>
-      </c>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>130215252</v>
       </c>
       <c r="B9" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>130214040</v>
       </c>
       <c r="B10" t="n">
-        <v>96059</v>
+        <v>96146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>130213978</v>
       </c>
       <c r="B11" t="n">
-        <v>97710</v>
+        <v>97797</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 14999-2024 artfynd.xlsx
+++ b/artfynd/A 14999-2024 artfynd.xlsx
@@ -1184,32 +1184,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130212863</v>
+        <v>130213671</v>
       </c>
       <c r="B7" t="n">
-        <v>93035</v>
+        <v>105972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3100</v>
+        <v>221725</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>747530</v>
+        <v>747707</v>
       </c>
       <c r="R7" t="n">
-        <v>7456067</v>
+        <v>7456091</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1274,43 +1274,39 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jennifer Sondell</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
-        </is>
-      </c>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130213671</v>
+        <v>130212863</v>
       </c>
       <c r="B8" t="n">
-        <v>105972</v>
+        <v>93035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221725</v>
+        <v>3100</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1320,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>747707</v>
+        <v>747530</v>
       </c>
       <c r="R8" t="n">
-        <v>7456091</v>
+        <v>7456067</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1375,10 +1371,14 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Irma Lindfors</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Jennifer Sondell</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">

--- a/artfynd/A 14999-2024 artfynd.xlsx
+++ b/artfynd/A 14999-2024 artfynd.xlsx
@@ -1184,32 +1184,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130213671</v>
+        <v>130212863</v>
       </c>
       <c r="B7" t="n">
-        <v>105972</v>
+        <v>93035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221725</v>
+        <v>3100</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>747707</v>
+        <v>747530</v>
       </c>
       <c r="R7" t="n">
-        <v>7456091</v>
+        <v>7456067</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1274,39 +1274,43 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Irma Lindfors</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Jennifer Sondell</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130212863</v>
+        <v>130213671</v>
       </c>
       <c r="B8" t="n">
-        <v>93035</v>
+        <v>105972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3100</v>
+        <v>221725</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>747530</v>
+        <v>747707</v>
       </c>
       <c r="R8" t="n">
-        <v>7456067</v>
+        <v>7456091</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1371,14 +1375,10 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jennifer Sondell</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
-        </is>
-      </c>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">

--- a/artfynd/A 14999-2024 artfynd.xlsx
+++ b/artfynd/A 14999-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>130215155</v>
       </c>
       <c r="B3" t="n">
-        <v>80313</v>
+        <v>80316</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>130213934</v>
       </c>
       <c r="B4" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>130215250</v>
       </c>
       <c r="B5" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>130213901</v>
       </c>
       <c r="B6" t="n">
-        <v>96158</v>
+        <v>96161</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>130212863</v>
       </c>
       <c r="B7" t="n">
-        <v>93035</v>
+        <v>93038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>130213671</v>
       </c>
       <c r="B8" t="n">
-        <v>105972</v>
+        <v>105975</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>130215252</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>130214040</v>
       </c>
       <c r="B10" t="n">
-        <v>96146</v>
+        <v>96149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>130213978</v>
       </c>
       <c r="B11" t="n">
-        <v>97797</v>
+        <v>97800</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 14999-2024 artfynd.xlsx
+++ b/artfynd/A 14999-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>130215155</v>
       </c>
       <c r="B3" t="n">
-        <v>80316</v>
+        <v>80342</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>130213934</v>
       </c>
       <c r="B4" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>130215250</v>
       </c>
       <c r="B5" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>130213901</v>
       </c>
       <c r="B6" t="n">
-        <v>96161</v>
+        <v>96187</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>130212863</v>
       </c>
       <c r="B7" t="n">
-        <v>93038</v>
+        <v>93064</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>130213671</v>
       </c>
       <c r="B8" t="n">
-        <v>105975</v>
+        <v>106001</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>130215252</v>
       </c>
       <c r="B9" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>130214040</v>
       </c>
       <c r="B10" t="n">
-        <v>96149</v>
+        <v>96175</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>130213978</v>
       </c>
       <c r="B11" t="n">
-        <v>97800</v>
+        <v>97826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 14999-2024 artfynd.xlsx
+++ b/artfynd/A 14999-2024 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>130213934</v>
       </c>
       <c r="B4" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>130215250</v>
       </c>
       <c r="B5" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>130213901</v>
       </c>
       <c r="B6" t="n">
-        <v>96187</v>
+        <v>96188</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>130212863</v>
       </c>
       <c r="B7" t="n">
-        <v>93064</v>
+        <v>93065</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>130213671</v>
       </c>
       <c r="B8" t="n">
-        <v>106001</v>
+        <v>106002</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>130214040</v>
       </c>
       <c r="B10" t="n">
-        <v>96175</v>
+        <v>96176</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>130213978</v>
       </c>
       <c r="B11" t="n">
-        <v>97826</v>
+        <v>97827</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 14999-2024 artfynd.xlsx
+++ b/artfynd/A 14999-2024 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>130213934</v>
       </c>
       <c r="B4" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>130215250</v>
       </c>
       <c r="B5" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>130213901</v>
       </c>
       <c r="B6" t="n">
-        <v>96188</v>
+        <v>96189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,32 +1184,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130212863</v>
+        <v>130213671</v>
       </c>
       <c r="B7" t="n">
-        <v>93065</v>
+        <v>106003</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3100</v>
+        <v>221725</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>747530</v>
+        <v>747707</v>
       </c>
       <c r="R7" t="n">
-        <v>7456067</v>
+        <v>7456091</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1274,43 +1274,39 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jennifer Sondell</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
-        </is>
-      </c>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130213671</v>
+        <v>130212863</v>
       </c>
       <c r="B8" t="n">
-        <v>106002</v>
+        <v>93066</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221725</v>
+        <v>3100</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1320,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>747707</v>
+        <v>747530</v>
       </c>
       <c r="R8" t="n">
-        <v>7456091</v>
+        <v>7456067</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1375,10 +1371,14 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Irma Lindfors</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Jennifer Sondell</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1486,7 +1486,7 @@
         <v>130214040</v>
       </c>
       <c r="B10" t="n">
-        <v>96176</v>
+        <v>96177</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>130213978</v>
       </c>
       <c r="B11" t="n">
-        <v>97827</v>
+        <v>97828</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 14999-2024 artfynd.xlsx
+++ b/artfynd/A 14999-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>130215155</v>
       </c>
       <c r="B3" t="n">
-        <v>80342</v>
+        <v>80344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>130213934</v>
       </c>
       <c r="B4" t="n">
-        <v>97822</v>
+        <v>97824</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>130215250</v>
       </c>
       <c r="B5" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>130213901</v>
       </c>
       <c r="B6" t="n">
-        <v>96189</v>
+        <v>96191</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>130213671</v>
       </c>
       <c r="B7" t="n">
-        <v>106003</v>
+        <v>106005</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>130212863</v>
       </c>
       <c r="B8" t="n">
-        <v>93066</v>
+        <v>93068</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>130215252</v>
       </c>
       <c r="B9" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>130214040</v>
       </c>
       <c r="B10" t="n">
-        <v>96177</v>
+        <v>96179</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>130213978</v>
       </c>
       <c r="B11" t="n">
-        <v>97828</v>
+        <v>97830</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 14999-2024 artfynd.xlsx
+++ b/artfynd/A 14999-2024 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>130213934</v>
       </c>
       <c r="B4" t="n">
-        <v>97824</v>
+        <v>97828</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>130213901</v>
       </c>
       <c r="B6" t="n">
-        <v>96191</v>
+        <v>96195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,32 +1184,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130213671</v>
+        <v>130212863</v>
       </c>
       <c r="B7" t="n">
-        <v>106005</v>
+        <v>93072</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221725</v>
+        <v>3100</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>747707</v>
+        <v>747530</v>
       </c>
       <c r="R7" t="n">
-        <v>7456091</v>
+        <v>7456067</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1274,39 +1274,43 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Irma Lindfors</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Jennifer Sondell</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130212863</v>
+        <v>130213671</v>
       </c>
       <c r="B8" t="n">
-        <v>93068</v>
+        <v>106009</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3100</v>
+        <v>221725</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>747530</v>
+        <v>747707</v>
       </c>
       <c r="R8" t="n">
-        <v>7456067</v>
+        <v>7456091</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1371,14 +1375,10 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jennifer Sondell</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
-        </is>
-      </c>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1486,7 +1486,7 @@
         <v>130214040</v>
       </c>
       <c r="B10" t="n">
-        <v>96179</v>
+        <v>96183</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>130213978</v>
       </c>
       <c r="B11" t="n">
-        <v>97830</v>
+        <v>97834</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 14999-2024 artfynd.xlsx
+++ b/artfynd/A 14999-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129683585</v>
+        <v>130211801</v>
       </c>
       <c r="B2" t="n">
-        <v>56921</v>
+        <v>101298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>1365</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gällivare, Lu lm</t>
+          <t>Gällivare kommun, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>748159</v>
+        <v>747542</v>
       </c>
       <c r="R2" t="n">
-        <v>7455853</v>
+        <v>7456225</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>06:15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>06:15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spårstämpel.</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +764,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Irma Lindfors</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Jennifer Sondell</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130215155</v>
+        <v>130211802</v>
       </c>
       <c r="B3" t="n">
-        <v>80344</v>
+        <v>101298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +791,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>1365</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gällivare kommun, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>747903</v>
+        <v>747527</v>
       </c>
       <c r="R3" t="n">
-        <v>7455922</v>
+        <v>7456225</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -882,7 +874,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hanna Vestman</t>
+          <t>Jennifer Sondell</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -893,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130213934</v>
+        <v>130211803</v>
       </c>
       <c r="B4" t="n">
-        <v>97828</v>
+        <v>101298</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,34 +896,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>1365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gällivare kommun, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>747737</v>
+        <v>747535</v>
       </c>
       <c r="R4" t="n">
-        <v>7456048</v>
+        <v>7456222</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -983,48 +979,60 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Irma Lindfors</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Jennifer Sondell</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130215250</v>
+        <v>130211804</v>
       </c>
       <c r="B5" t="n">
-        <v>91781</v>
+        <v>101298</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1365</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gällivare kommun, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>747925</v>
+        <v>747535</v>
       </c>
       <c r="R5" t="n">
-        <v>7455943</v>
+        <v>7456221</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1076,7 +1084,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hanna Vestman</t>
+          <t>Jennifer Sondell</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1087,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130213901</v>
+        <v>130211805</v>
       </c>
       <c r="B6" t="n">
-        <v>96195</v>
+        <v>101298</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,34 +1106,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2813</v>
+        <v>1365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gällivare kommun, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>747739</v>
+        <v>747524</v>
       </c>
       <c r="R6" t="n">
-        <v>7456070</v>
+        <v>7456221</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1177,52 +1189,60 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Irma Lindfors</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Jennifer Sondell</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130212863</v>
+        <v>130211806</v>
       </c>
       <c r="B7" t="n">
-        <v>93072</v>
+        <v>101298</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3100</v>
+        <v>1365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gällivare kommun, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>747530</v>
+        <v>747533</v>
       </c>
       <c r="R7" t="n">
-        <v>7456067</v>
+        <v>7456217</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1285,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130213671</v>
+        <v>130214040</v>
       </c>
       <c r="B8" t="n">
-        <v>106009</v>
+        <v>96338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1296,21 +1316,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221725</v>
+        <v>2809</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1320,10 +1340,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>747707</v>
+        <v>747784</v>
       </c>
       <c r="R8" t="n">
-        <v>7456091</v>
+        <v>7456011</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1350,12 +1370,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1382,32 +1402,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130215252</v>
+        <v>130213901</v>
       </c>
       <c r="B9" t="n">
-        <v>79211</v>
+        <v>96350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2813</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>747913</v>
+        <v>747739</v>
       </c>
       <c r="R9" t="n">
-        <v>7455917</v>
+        <v>7456070</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1472,43 +1492,39 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hanna Vestman</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
-        </is>
-      </c>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130214040</v>
+        <v>130212863</v>
       </c>
       <c r="B10" t="n">
-        <v>96183</v>
+        <v>93222</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2809</v>
+        <v>3100</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1534,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>747784</v>
+        <v>747530</v>
       </c>
       <c r="R10" t="n">
-        <v>7456011</v>
+        <v>7456067</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1548,12 +1564,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1573,39 +1589,43 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Irma Lindfors</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Jennifer Sondell</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130213978</v>
+        <v>130213705</v>
       </c>
       <c r="B11" t="n">
-        <v>97834</v>
+        <v>89156</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>4412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1615,10 +1635,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>747720</v>
+        <v>747797</v>
       </c>
       <c r="R11" t="n">
-        <v>7456169</v>
+        <v>7456191</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1674,6 +1694,935 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130215252</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>747913</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7455917</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Hanna Vestman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130213138</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80460</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>747505</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7456197</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jennifer Sondell</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130215155</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80460</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>747903</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7455922</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Hanna Vestman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129683585</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gällivare, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>748159</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7455853</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>06:15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>06:15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Spårstämpel.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129683586</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gällivare, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>748062</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7456030</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>06:06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>06:06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Spårstämpel.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130213671</v>
+      </c>
+      <c r="B17" t="n">
+        <v>106228</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>747707</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7456091</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130213978</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>747720</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7456169</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130213934</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>747737</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7456048</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130215114</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>747895</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7455904</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Hanna Vestman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14999-2024 artfynd.xlsx
+++ b/artfynd/A 14999-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
           <t>Tillståndskonsulter Naalojärvi-Messaure</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130211801</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
           <t>Tillståndskonsulter Naalojärvi-Messaure</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130211802</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
           <t>Tillståndskonsulter Naalojärvi-Messaure</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130211803</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
           <t>Tillståndskonsulter Naalojärvi-Messaure</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130211804</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
           <t>Tillståndskonsulter Naalojärvi-Messaure</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130211805</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
           <t>Tillståndskonsulter Naalojärvi-Messaure</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130211806</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1399,6 +1434,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130214040</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1496,6 +1536,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130213901</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1597,6 +1642,11 @@
           <t>Tillståndskonsulter Naalojärvi-Messaure</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130212863</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1694,6 +1744,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130213705</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1795,6 +1850,11 @@
           <t>Tillståndskonsulter Naalojärvi-Messaure</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130215252</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
           <t>Tillståndskonsulter Naalojärvi-Messaure</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130213138</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1997,6 +2062,11 @@
           <t>Tillståndskonsulter Naalojärvi-Messaure</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130215155</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2114,6 +2184,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129683585</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2231,6 +2306,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129683586</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2328,6 +2408,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130213671</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2425,6 +2510,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130213978</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2522,6 +2612,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130213934</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2623,8 +2718,34 @@
           <t>Tillståndskonsulter Naalojärvi-Messaure</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130215114</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>